--- a/artfynd/A 4620-2024 artfynd.xlsx
+++ b/artfynd/A 4620-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440157</v>
       </c>
       <c r="B2" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136440154</v>
       </c>
       <c r="B3" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4620-2024 artfynd.xlsx
+++ b/artfynd/A 4620-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440157</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136440154</v>
       </c>
       <c r="B3" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4620-2024 artfynd.xlsx
+++ b/artfynd/A 4620-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440157</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136440154</v>
       </c>
       <c r="B3" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4620-2024 artfynd.xlsx
+++ b/artfynd/A 4620-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440157</v>
       </c>
       <c r="B2" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136440154</v>
       </c>
       <c r="B3" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4620-2024 artfynd.xlsx
+++ b/artfynd/A 4620-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440157</v>
       </c>
       <c r="B2" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136440154</v>
       </c>
       <c r="B3" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4620-2024 artfynd.xlsx
+++ b/artfynd/A 4620-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440157</v>
       </c>
       <c r="B2" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136440154</v>
       </c>
       <c r="B3" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4620-2024 artfynd.xlsx
+++ b/artfynd/A 4620-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440157</v>
       </c>
       <c r="B2" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136440154</v>
       </c>
       <c r="B3" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
